--- a/sheets/민요/검수/흥 타령 (채보3).xlsx
+++ b/sheets/민요/검수/흥 타령 (채보3).xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/흥 타령 (채보3).xlsx
+++ b/sheets/민요/검수/흥 타령 (채보3).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3805,98 +3849,98 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">흥 타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">땅</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">잔</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">땅</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="N3" s="18" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
@@ -3904,73 +3948,73 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">속</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">속</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="N4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -3978,78 +4022,78 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">쁜</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="K5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">쁜</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr">
+      <c r="M5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="O5" s="10" t="inlineStr">
+      <c r="O5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">람</t>
         </is>
@@ -4057,74 +4101,74 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">뻐</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">습</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">뻐</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">누</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="N6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4132,64 +4176,64 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E7" s="25"/>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G7" s="25"/>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">웠</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="N7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">묻</t>
         </is>
@@ -4197,64 +4241,64 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">문</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="26"/>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="26"/>
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">문</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="K8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">습</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">느</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O8" s="10" t="inlineStr">
+      <c r="N8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">혀</t>
         </is>
@@ -4262,73 +4306,73 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">혀</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">혀</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">있</t>
         </is>
@@ -4336,63 +4380,63 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C10" s="25"/>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E10" s="25"/>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G10" s="25"/>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="M10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="O10" s="9" t="inlineStr">
+      <c r="O10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -4400,64 +4444,64 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C11" s="26"/>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E11" s="26"/>
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="26"/>
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="K11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="O11" s="10" t="inlineStr">
+      <c r="O11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4465,62 +4509,62 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C12" s="24"/>
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="24"/>
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="G12" s="24"/>
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="M12" s="8"/>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="M12" s="24"/>
+      <c r="N12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4528,118 +4572,118 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C13" s="25"/>
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="25"/>
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O13" s="9"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C14" s="26"/>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="26"/>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">어도</t>
         </is>
       </c>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="26"/>
+      <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O14" s="10"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O14" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/흥 타령 (채보3).xlsx
+++ b/sheets/민요/검수/흥 타령 (채보3).xlsx
@@ -3828,26 +3828,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3868,11 +3868,11 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -3946,11 +3946,11 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C4" s="25" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="D4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E4" s="25" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="F4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="N4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O4" s="25" t="inlineStr">
@@ -4020,11 +4020,11 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">
@@ -4099,11 +4099,11 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="N6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O6" s="24" t="inlineStr">
@@ -4174,11 +4174,11 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C7" s="25" t="inlineStr">
@@ -4188,19 +4188,19 @@
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G7" s="25"/>
       <c r="H7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="25" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="N7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O7" s="25" t="inlineStr">
@@ -4239,11 +4239,11 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C8" s="26" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="N8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O8" s="26" t="inlineStr">
@@ -4304,11 +4304,11 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G9" s="24" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I9" s="24" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="J9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K9" s="24" t="inlineStr">
@@ -4378,29 +4378,29 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C10" s="25"/>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E10" s="25"/>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G10" s="25"/>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="25" t="inlineStr">
@@ -4442,17 +4442,17 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C11" s="26"/>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E11" s="26"/>
@@ -4507,11 +4507,11 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C12" s="24"/>
@@ -4570,11 +4570,11 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C13" s="25"/>
@@ -4623,16 +4623,16 @@
       <c r="M13" s="25"/>
       <c r="N13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C14" s="26"/>
@@ -4680,7 +4680,7 @@
       <c r="M14" s="26"/>
       <c r="N14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O14" s="26"/>

--- a/sheets/민요/검수/흥 타령 (채보3).xlsx
+++ b/sheets/민요/검수/흥 타령 (채보3).xlsx
@@ -4662,7 +4662,8 @@
       </c>
       <c r="I14" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">어도</t>
+          <t xml:space="preserve">어
+도</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">

--- a/sheets/민요/검수/흥 타령 (채보3).xlsx
+++ b/sheets/민요/검수/흥 타령 (채보3).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -239,6 +244,24 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3875,7 +3898,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">땅</t>
         </is>
@@ -3886,7 +3909,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">잔</t>
         </is>
@@ -3896,7 +3919,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -3907,7 +3930,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">땅</t>
         </is>
@@ -3918,7 +3941,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K3" s="24" t="inlineStr">
+      <c r="K3" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -3929,7 +3952,7 @@
 潢</t>
         </is>
       </c>
-      <c r="M3" s="24" t="inlineStr">
+      <c r="M3" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
@@ -3940,7 +3963,7 @@
 潢</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
@@ -3953,7 +3976,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">속</t>
         </is>
@@ -3963,7 +3986,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -3973,7 +3996,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
@@ -3983,7 +4006,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">속</t>
         </is>
@@ -3993,7 +4016,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
@@ -4004,7 +4027,7 @@
 潢</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4014,7 +4037,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O4" s="25" t="inlineStr">
+      <c r="O4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -4027,7 +4050,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4038,7 +4061,7 @@
 南</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
@@ -4049,7 +4072,7 @@
 南</t>
         </is>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">쁜</t>
         </is>
@@ -4060,7 +4083,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4071,7 +4094,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K5" s="26" t="inlineStr">
+      <c r="K5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">쁜</t>
         </is>
@@ -4082,7 +4105,7 @@
 潢</t>
         </is>
       </c>
-      <c r="M5" s="26" t="inlineStr">
+      <c r="M5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4093,7 +4116,7 @@
 潢</t>
         </is>
       </c>
-      <c r="O5" s="26" t="inlineStr">
+      <c r="O5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">람</t>
         </is>
@@ -4106,7 +4129,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">뻐</t>
         </is>
@@ -4116,7 +4139,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4126,7 +4149,7 @@
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="G6" s="29" t="inlineStr">
+      <c r="G6" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">습</t>
         </is>
@@ -4137,7 +4160,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">뻐</t>
         </is>
@@ -4147,7 +4170,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K6" s="24" t="inlineStr">
+      <c r="K6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
@@ -4158,7 +4181,7 @@
 潢</t>
         </is>
       </c>
-      <c r="M6" s="24" t="inlineStr">
+      <c r="M6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">누</t>
         </is>
@@ -4168,7 +4191,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O6" s="24" t="inlineStr">
+      <c r="O6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4181,7 +4204,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
@@ -4191,19 +4214,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E7" s="25"/>
+      <c r="E7" s="32"/>
       <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G7" s="25"/>
+      <c r="G7" s="32"/>
       <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
@@ -4213,7 +4236,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K7" s="25" t="inlineStr">
+      <c r="K7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
@@ -4223,7 +4246,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M7" s="25" t="inlineStr">
+      <c r="M7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">웠</t>
         </is>
@@ -4233,7 +4256,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O7" s="25" t="inlineStr">
+      <c r="O7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">묻</t>
         </is>
@@ -4246,7 +4269,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">문</t>
         </is>
@@ -4256,19 +4279,19 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E8" s="26"/>
+      <c r="E8" s="33"/>
       <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I8" s="26" t="inlineStr">
+      <c r="I8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">문</t>
         </is>
@@ -4278,7 +4301,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K8" s="26" t="inlineStr">
+      <c r="K8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">습</t>
         </is>
@@ -4288,7 +4311,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M8" s="26" t="inlineStr">
+      <c r="M8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">느</t>
         </is>
@@ -4298,7 +4321,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O8" s="26" t="inlineStr">
+      <c r="O8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">혀</t>
         </is>
@@ -4311,7 +4334,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">혀</t>
         </is>
@@ -4321,7 +4344,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4331,7 +4354,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4341,7 +4364,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I9" s="24" t="inlineStr">
+      <c r="I9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">혀</t>
         </is>
@@ -4351,7 +4374,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K9" s="24" t="inlineStr">
+      <c r="K9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -4361,7 +4384,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M9" s="24" t="inlineStr">
+      <c r="M9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4372,7 +4395,7 @@
 潢</t>
         </is>
       </c>
-      <c r="O9" s="24" t="inlineStr">
+      <c r="O9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">있</t>
         </is>
@@ -4385,25 +4408,25 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C10" s="25"/>
+      <c r="C10" s="32"/>
       <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E10" s="25"/>
+      <c r="E10" s="32"/>
       <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G10" s="25"/>
+      <c r="G10" s="32"/>
       <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4414,7 +4437,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K10" s="25" t="inlineStr">
+      <c r="K10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -4425,7 +4448,7 @@
 潢</t>
         </is>
       </c>
-      <c r="M10" s="25" t="inlineStr">
+      <c r="M10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4436,7 +4459,7 @@
 姑</t>
         </is>
       </c>
-      <c r="O10" s="25" t="inlineStr">
+      <c r="O10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -4449,26 +4472,26 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C11" s="26"/>
+      <c r="C11" s="33"/>
       <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E11" s="26"/>
+      <c r="E11" s="33"/>
       <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="G11" s="26"/>
+      <c r="G11" s="33"/>
       <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I11" s="26" t="inlineStr">
+      <c r="I11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
@@ -4479,7 +4502,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K11" s="26" t="inlineStr">
+      <c r="K11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4490,7 +4513,7 @@
 潢</t>
         </is>
       </c>
-      <c r="M11" s="26" t="inlineStr">
+      <c r="M11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4501,7 +4524,7 @@
 汰</t>
         </is>
       </c>
-      <c r="O11" s="26" t="inlineStr">
+      <c r="O11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4514,28 +4537,28 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="24"/>
+      <c r="C12" s="31"/>
       <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="E12" s="24"/>
+      <c r="E12" s="31"/>
       <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="G12" s="24"/>
+      <c r="G12" s="31"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
@@ -4546,7 +4569,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K12" s="24" t="inlineStr">
+      <c r="K12" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -4557,14 +4580,14 @@
 潢</t>
         </is>
       </c>
-      <c r="M12" s="24"/>
+      <c r="M12" s="31"/>
       <c r="N12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="O12" s="24" t="inlineStr">
+      <c r="O12" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4577,19 +4600,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="25"/>
+      <c r="C13" s="32"/>
       <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E13" s="25"/>
+      <c r="E13" s="32"/>
       <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -4599,7 +4622,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I13" s="25" t="inlineStr">
+      <c r="I13" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
@@ -4609,7 +4632,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="K13" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -4620,13 +4643,13 @@
 姑</t>
         </is>
       </c>
-      <c r="M13" s="25"/>
+      <c r="M13" s="32"/>
       <c r="N13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O13" s="25"/>
+      <c r="O13" s="32"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
@@ -4635,21 +4658,21 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="26"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="E14" s="26"/>
+      <c r="E14" s="33"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="G14" s="26" t="inlineStr">
+      <c r="G14" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -4660,7 +4683,7 @@
 姑</t>
         </is>
       </c>
-      <c r="I14" s="26" t="inlineStr">
+      <c r="I14" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">어
 도</t>
@@ -4672,19 +4695,19 @@
 姑</t>
         </is>
       </c>
-      <c r="K14" s="26"/>
+      <c r="K14" s="33"/>
       <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M14" s="26"/>
+      <c r="M14" s="33"/>
       <c r="N14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O14" s="26"/>
+      <c r="O14" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="1">
